--- a/data/CIGRE_HV_Network_Input.xlsx
+++ b/data/CIGRE_HV_Network_Input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_market_model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_MPEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D2BD56-9409-4591-97FF-EFE5C057F451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061347DB-5FEB-456D-AADE-B790CEBE39D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="3090" windowWidth="30075" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -786,14 +786,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,14 +1097,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:F67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:6" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="13"/>
@@ -1112,278 +1112,278 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B45" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B48" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B67" s="14" t="s">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B67" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C67" s="13"/>
@@ -1413,20 +1413,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:L21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C2" s="13"/>
@@ -1440,7 +1440,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>57</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="7">
         <v>10</v>
       </c>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>11</v>
       </c>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="7">
         <v>12</v>
       </c>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>13</v>
       </c>
@@ -1904,8 +1904,8 @@
       </c>
       <c r="L17" s="2"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B21" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="13"/>
@@ -1931,7 +1931,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:O17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1947,8 +1947,8 @@
     <col min="15" max="15" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="13"/>
@@ -1965,7 +1965,7 @@
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
     </row>
-    <row r="4" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>85</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -2387,8 +2387,8 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C17" s="13"/>
@@ -2417,7 +2417,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:V14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2437,8 +2437,8 @@
     <col min="22" max="22" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:22" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>105</v>
       </c>
       <c r="C2" s="13"/>
@@ -2462,7 +2462,7 @@
       <c r="U2" s="13"/>
       <c r="V2" s="13"/>
     </row>
-    <row r="4" spans="2:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>106</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2571,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="5">
         <v>0</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2634,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="7">
         <v>0</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="V6" s="8"/>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="5">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>124</v>
@@ -2697,10 +2697,10 @@
         <v>0</v>
       </c>
       <c r="P7" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="5">
         <v>0</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>124</v>
@@ -2760,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="V8" s="8"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="5">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>124</v>
@@ -2823,10 +2823,10 @@
         <v>0</v>
       </c>
       <c r="P9" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="5">
         <v>0</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="7">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>124</v>
@@ -2886,10 +2886,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q10" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="7">
         <v>0</v>
@@ -2905,8 +2905,8 @@
       </c>
       <c r="V10" s="8"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B14" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="13"/>
@@ -2942,7 +2942,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:L15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2953,8 +2953,8 @@
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>130</v>
       </c>
       <c r="C2" s="13"/>
@@ -2968,7 +2968,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>131</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="10" t="s">
         <v>143</v>
       </c>
@@ -3179,8 +3179,8 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B15" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C15" s="13"/>
@@ -3206,18 +3206,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:S11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" customWidth="1"/>
+    <col min="8" max="9" width="11.453125" customWidth="1"/>
     <col min="10" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:19" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>144</v>
       </c>
       <c r="C2" s="13"/>
@@ -3238,7 +3238,7 @@
       <c r="R2" s="13"/>
       <c r="S2" s="13"/>
     </row>
-    <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="S6" s="8"/>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3456,8 +3456,8 @@
       </c>
       <c r="S7" s="2"/>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B11" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="13"/>
@@ -3490,7 +3490,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:R9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3504,8 +3504,8 @@
     <col min="18" max="18" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>158</v>
       </c>
       <c r="C2" s="13"/>
@@ -3525,7 +3525,7 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="4" spans="2:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>159</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3629,8 +3629,8 @@
       </c>
       <c r="R5" s="2"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B9" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C9" s="13"/>
@@ -3662,7 +3662,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:L13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3673,8 +3673,8 @@
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>164</v>
       </c>
       <c r="C2" s="13"/>
@@ -3688,7 +3688,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>165</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
         <v>171</v>
       </c>
@@ -3830,8 +3830,8 @@
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B13" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="13"/>
@@ -3857,7 +3857,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3865,14 +3865,14 @@
     <col min="4" max="4" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>172</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
     </row>
-    <row r="4" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>173</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>176</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="8" t="s">
         <v>178</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>180</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" s="8" t="s">
         <v>182</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>184</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>187</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>190</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>193</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>195</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="8" t="s">
         <v>197</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>199</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="8" t="s">
         <v>201</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>203</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="8" t="s">
         <v>205</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>208</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="8" t="s">
         <v>210</v>
       </c>
@@ -4059,8 +4059,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="14" t="s">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="13"/>

--- a/data/CIGRE_HV_Network_Input.xlsx
+++ b/data/CIGRE_HV_Network_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_MPEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061347DB-5FEB-456D-AADE-B790CEBE39D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA4861D-256C-4A82-B05A-BE037C3D198C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="216">
   <si>
     <t>CIGRE European HV 13-Bus Benchmark — Dual-Price Stackelberg Reactive Power Market</t>
   </si>
@@ -519,9 +519,6 @@
     <t>slack_weight</t>
   </si>
   <si>
-    <t>ExtGrid_B9</t>
-  </si>
-  <si>
     <t>CIGRE HV — Shunt Data  (positive q_mvar = capacitive injection; pandapower sign reversed)</t>
   </si>
   <si>
@@ -673,6 +670,12 @@
   </si>
   <si>
     <t>max_p_mw</t>
+  </si>
+  <si>
+    <t>Gen_9</t>
+  </si>
+  <si>
+    <t>ExtGrid</t>
   </si>
 </sst>
 </file>
@@ -757,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -794,6 +797,9 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,13 +1103,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:F67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -1112,277 +1118,277 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67" s="12" t="s">
         <v>55</v>
       </c>
@@ -1413,19 +1419,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:L21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>56</v>
       </c>
@@ -1440,7 +1446,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>57</v>
       </c>
@@ -1475,7 +1481,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -1508,7 +1514,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -1541,7 +1547,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -1574,7 +1580,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -1607,7 +1613,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1640,7 +1646,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -1673,7 +1679,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -1706,7 +1712,7 @@
       </c>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -1739,7 +1745,7 @@
       </c>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -1772,7 +1778,7 @@
       </c>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="7">
         <v>10</v>
       </c>
@@ -1805,7 +1811,7 @@
       </c>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>11</v>
       </c>
@@ -1838,7 +1844,7 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="7">
         <v>12</v>
       </c>
@@ -1871,7 +1877,7 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>13</v>
       </c>
@@ -1904,7 +1910,7 @@
       </c>
       <c r="L17" s="2"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
         <v>55</v>
       </c>
@@ -1931,7 +1937,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:O17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1947,7 +1953,7 @@
     <col min="15" max="15" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>84</v>
       </c>
@@ -1965,7 +1971,7 @@
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
     </row>
-    <row r="4" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>85</v>
       </c>
@@ -2009,7 +2015,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2051,7 +2057,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2093,7 +2099,7 @@
       </c>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2135,7 +2141,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2177,7 +2183,7 @@
       </c>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2219,7 +2225,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2261,7 +2267,7 @@
       </c>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -2303,7 +2309,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -2345,7 +2351,7 @@
       </c>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -2387,7 +2393,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
         <v>55</v>
       </c>
@@ -2417,7 +2423,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:V14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2437,7 +2443,7 @@
     <col min="22" max="22" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:22" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>105</v>
       </c>
@@ -2462,7 +2468,7 @@
       <c r="U2" s="13"/>
       <c r="V2" s="13"/>
     </row>
-    <row r="4" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>106</v>
       </c>
@@ -2527,7 +2533,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2590,7 +2596,7 @@
       </c>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2653,7 +2659,7 @@
       </c>
       <c r="V6" s="8"/>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2716,7 +2722,7 @@
       </c>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2779,7 +2785,7 @@
       </c>
       <c r="V8" s="8"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2842,7 +2848,7 @@
       </c>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2905,7 +2911,7 @@
       </c>
       <c r="V10" s="8"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
         <v>55</v>
       </c>
@@ -2942,7 +2948,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2953,7 +2959,7 @@
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>130</v>
       </c>
@@ -2968,7 +2974,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>131</v>
       </c>
@@ -3003,7 +3009,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3036,7 +3042,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3069,7 +3075,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3102,7 +3108,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -3135,7 +3141,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -3168,7 +3174,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>143</v>
       </c>
@@ -3179,7 +3185,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>55</v>
       </c>
@@ -3206,17 +3212,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:S11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="11.453125" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" customWidth="1"/>
     <col min="10" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>144</v>
       </c>
@@ -3238,7 +3244,7 @@
       <c r="R2" s="13"/>
       <c r="S2" s="13"/>
     </row>
-    <row r="4" spans="2:19" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
@@ -3258,10 +3264,10 @@
         <v>146</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>147</v>
@@ -3294,169 +3300,223 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5" s="5">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="C5" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="7">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7">
         <v>500</v>
       </c>
-      <c r="F5" s="5">
-        <v>150</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="7">
+        <v>200</v>
+      </c>
+      <c r="G5" s="7">
         <v>1.03</v>
       </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>600</v>
-      </c>
-      <c r="J5" s="5">
-        <v>-250</v>
-      </c>
-      <c r="K5" s="5">
-        <v>360</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>750</v>
+      </c>
+      <c r="J5" s="7">
+        <v>-350</v>
+      </c>
+      <c r="K5" s="7">
+        <v>500</v>
+      </c>
+      <c r="L5" s="7">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="N5" s="7">
+        <v>5</v>
+      </c>
+      <c r="O5" s="7">
         <v>1E-3</v>
       </c>
-      <c r="M5" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="N5" s="5">
-        <v>8</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1.5E-3</v>
-      </c>
-      <c r="P5" s="5">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>10</v>
-      </c>
-      <c r="R5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="P5" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>6</v>
+      </c>
+      <c r="R5" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="8"/>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="7">
-        <v>12</v>
-      </c>
-      <c r="E6" s="7">
-        <v>200</v>
-      </c>
-      <c r="F6" s="7">
-        <v>200</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="C6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="5">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5">
+        <v>500</v>
+      </c>
+      <c r="F6" s="5">
+        <v>150</v>
+      </c>
+      <c r="G6" s="5">
         <v>1.03</v>
       </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>500</v>
-      </c>
-      <c r="J6" s="7">
-        <v>-170</v>
-      </c>
-      <c r="K6" s="7">
-        <v>250</v>
-      </c>
-      <c r="L6" s="7">
-        <v>1.8E-3</v>
-      </c>
-      <c r="M6" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="N6" s="7">
-        <v>6</v>
-      </c>
-      <c r="O6" s="7">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="P6" s="7">
-        <v>1.75</v>
-      </c>
-      <c r="Q6" s="7">
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>600</v>
+      </c>
+      <c r="J6" s="5">
+        <v>-250</v>
+      </c>
+      <c r="K6" s="5">
+        <v>360</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="N6" s="5">
         <v>8</v>
       </c>
-      <c r="R6" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="8"/>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="O6" s="5">
+        <v>1.5E-3</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>10</v>
+      </c>
+      <c r="R6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="7">
+        <v>12</v>
+      </c>
+      <c r="E7" s="7">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7">
+        <v>200</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1.03</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>500</v>
+      </c>
+      <c r="J7" s="7">
+        <v>-170</v>
+      </c>
+      <c r="K7" s="7">
+        <v>250</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1.8E-3</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="N7" s="7">
+        <v>6</v>
+      </c>
+      <c r="O7" s="7">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="P7" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>8</v>
+      </c>
+      <c r="R7" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="8"/>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B8" s="7">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D8" s="5">
         <v>13</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E8" s="5">
         <v>300</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F8" s="5">
         <v>170</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G8" s="5">
         <v>1.03</v>
       </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
         <v>450</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J8" s="5">
         <v>-150</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K8" s="5">
         <v>220</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L8" s="5">
         <v>1.5E-3</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M8" s="5">
         <v>1.2</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N8" s="5">
         <v>7</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O8" s="5">
         <v>2E-3</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P8" s="5">
         <v>1.5</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q8" s="5">
         <v>9</v>
       </c>
-      <c r="R7" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="R8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5"/>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>55</v>
       </c>
@@ -3489,24 +3549,119 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:R9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="38" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="4" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="7">
+        <v>8</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="B2:L13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
-    <col min="18" max="18" width="38" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -3518,16 +3673,10 @@
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-    </row>
-    <row r="4" spans="2:18" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>58</v>
@@ -3536,169 +3685,6 @@
         <v>57</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D5" s="5">
-        <v>10</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>-350</v>
-      </c>
-      <c r="H5" s="5">
-        <v>500</v>
-      </c>
-      <c r="I5" s="5">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="K5" s="5">
-        <v>5</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="N5" s="5">
-        <v>6</v>
-      </c>
-      <c r="O5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" s="2"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B9" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B9:R9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B2:L13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="38" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-    </row>
-    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -3708,10 +3694,10 @@
         <v>59</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>161</v>
@@ -3723,12 +3709,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D5" s="5">
         <v>4</v>
@@ -3756,12 +3742,12 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D6" s="7">
         <v>5</v>
@@ -3789,12 +3775,12 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D7" s="5">
         <v>6</v>
@@ -3822,15 +3808,15 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E9" s="11">
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
         <v>55</v>
       </c>
@@ -3857,7 +3843,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:D24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3865,201 +3851,201 @@
     <col min="4" max="4" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
     </row>
-    <row r="4" spans="2:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="4" t="s">
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="C5" s="5">
         <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="8" t="s">
-        <v>178</v>
       </c>
       <c r="C6" s="7">
         <v>50</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="C7" s="5">
         <v>500</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8" t="s">
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="8" t="s">
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D11" s="2" t="s">
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="8" t="s">
-        <v>193</v>
       </c>
       <c r="C12" s="7">
         <v>3000</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="C13" s="5">
         <v>1E-8</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="8" t="s">
-        <v>197</v>
       </c>
       <c r="C14" s="7">
         <v>300</v>
       </c>
       <c r="D14" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="s">
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C16" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8" t="s">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="C17" s="5">
         <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="8" t="s">
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
         <v>55</v>
       </c>

--- a/data/CIGRE_HV_Network_Input.xlsx
+++ b/data/CIGRE_HV_Network_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_MPEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA4861D-256C-4A82-B05A-BE037C3D198C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F7B33B-1FF7-4C77-A8D6-164A1982896D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -789,11 +789,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1389,7 +1389,7 @@
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C67" s="13"/>
@@ -1432,7 +1432,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C2" s="13"/>
@@ -1911,7 +1911,7 @@
       <c r="L17" s="2"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="13"/>
@@ -1954,7 +1954,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="13"/>
@@ -2394,7 +2394,7 @@
       <c r="O13" s="2"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C17" s="13"/>
@@ -2444,7 +2444,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>105</v>
       </c>
       <c r="C2" s="13"/>
@@ -2912,7 +2912,7 @@
       <c r="V10" s="8"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="13"/>
@@ -2960,7 +2960,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>130</v>
       </c>
       <c r="C2" s="13"/>
@@ -3186,7 +3186,7 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C15" s="13"/>
@@ -3223,7 +3223,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>144</v>
       </c>
       <c r="C2" s="13"/>
@@ -3338,7 +3338,7 @@
         <v>0.7</v>
       </c>
       <c r="N5" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O5" s="7">
         <v>1E-3</v>
@@ -3347,7 +3347,7 @@
         <v>0.85</v>
       </c>
       <c r="Q5" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R5" s="9" t="b">
         <v>1</v>
@@ -3392,7 +3392,7 @@
         <v>0.9</v>
       </c>
       <c r="N6" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6" s="5">
         <v>1.5E-3</v>
@@ -3401,7 +3401,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="Q6" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R6" s="6" t="b">
         <v>1</v>
@@ -3446,7 +3446,7 @@
         <v>1.4</v>
       </c>
       <c r="N7" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O7" s="7">
         <v>2.5000000000000001E-3</v>
@@ -3455,7 +3455,7 @@
         <v>1.75</v>
       </c>
       <c r="Q7" s="7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R7" s="9" t="b">
         <v>1</v>
@@ -3500,7 +3500,7 @@
         <v>1.2</v>
       </c>
       <c r="N8" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O8" s="5">
         <v>2E-3</v>
@@ -3509,7 +3509,7 @@
         <v>1.5</v>
       </c>
       <c r="Q8" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6" t="b">
         <v>1</v>
@@ -3517,7 +3517,7 @@
       <c r="S8" s="5"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="13"/>
@@ -3625,7 +3625,7 @@
       <c r="I5" s="7"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C9" s="13"/>
@@ -3660,7 +3660,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C2" s="13"/>
@@ -3817,7 +3817,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="13"/>
@@ -3852,7 +3852,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>171</v>
       </c>
       <c r="C2" s="13"/>
@@ -4046,7 +4046,7 @@
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="13"/>

--- a/data/CIGRE_HV_Network_Input.xlsx
+++ b/data/CIGRE_HV_Network_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_MPEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F7B33B-1FF7-4C77-A8D6-164A1982896D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819C2D9E-8897-4EED-BF6F-2EF299C67BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3460" yWindow="4070" windowWidth="19200" windowHeight="11210" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1103,13 +1103,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:F67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -1118,277 +1118,277 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B45" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B48" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B67" s="14" t="s">
         <v>55</v>
       </c>
@@ -1419,19 +1419,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:L21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>56</v>
       </c>
@@ -1446,7 +1446,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>57</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="7">
         <v>10</v>
       </c>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>11</v>
       </c>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="7">
         <v>12</v>
       </c>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>13</v>
       </c>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L17" s="2"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="14" t="s">
         <v>55</v>
       </c>
@@ -1937,7 +1937,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:O17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1953,7 +1953,7 @@
     <col min="15" max="15" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>84</v>
       </c>
@@ -1971,7 +1971,7 @@
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
     </row>
-    <row r="4" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>85</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="14" t="s">
         <v>55</v>
       </c>
@@ -2423,7 +2423,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:V14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2443,7 +2443,7 @@
     <col min="22" max="22" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>105</v>
       </c>
@@ -2468,7 +2468,7 @@
       <c r="U2" s="13"/>
       <c r="V2" s="13"/>
     </row>
-    <row r="4" spans="2:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>106</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="V6" s="8"/>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="V8" s="8"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="V10" s="8"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B14" s="14" t="s">
         <v>55</v>
       </c>
@@ -2948,7 +2948,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:L15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2959,7 +2959,7 @@
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>130</v>
       </c>
@@ -2974,7 +2974,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>131</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="10" t="s">
         <v>143</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="14" t="s">
         <v>55</v>
       </c>
@@ -3212,17 +3212,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:S11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" customWidth="1"/>
+    <col min="8" max="9" width="11.453125" customWidth="1"/>
     <col min="10" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>144</v>
       </c>
@@ -3244,7 +3244,7 @@
       <c r="R2" s="13"/>
       <c r="S2" s="13"/>
     </row>
-    <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3341,10 +3341,10 @@
         <v>0</v>
       </c>
       <c r="O5" s="7">
-        <v>1E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="P5" s="7">
-        <v>0.85</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="S5" s="8"/>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3386,10 +3386,10 @@
         <v>360</v>
       </c>
       <c r="L6" s="5">
-        <v>1E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="M6" s="5">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="N6" s="5">
         <v>0</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="S6" s="5"/>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="S7" s="8"/>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -3494,10 +3494,10 @@
         <v>220</v>
       </c>
       <c r="L8" s="5">
-        <v>1.5E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="M8" s="5">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N8" s="5">
         <v>0</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="S8" s="5"/>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B11" s="14" t="s">
         <v>55</v>
       </c>
@@ -3550,19 +3550,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:I9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" customWidth="1"/>
+    <col min="8" max="8" width="17.453125" customWidth="1"/>
     <col min="9" max="9" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>158</v>
       </c>
@@ -3574,7 +3574,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
-    <row r="4" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>159</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="7">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="F5" s="7">
         <v>0</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="14" t="s">
         <v>55</v>
       </c>
@@ -3648,7 +3648,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:L13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3659,7 +3659,7 @@
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>163</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>164</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
         <v>170</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
         <v>55</v>
       </c>
@@ -3843,7 +3843,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3851,14 +3851,14 @@
     <col min="4" max="4" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>171</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
     </row>
-    <row r="4" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>172</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>175</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="8" t="s">
         <v>177</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>179</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" s="8" t="s">
         <v>181</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>183</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>186</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>189</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>192</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>194</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="8" t="s">
         <v>196</v>
       </c>
@@ -3979,7 +3979,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>198</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="8" t="s">
         <v>200</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>202</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="8" t="s">
         <v>204</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>207</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="8" t="s">
         <v>209</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="14" t="s">
         <v>55</v>
       </c>

--- a/data/CIGRE_HV_Network_Input.xlsx
+++ b/data/CIGRE_HV_Network_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_MPEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819C2D9E-8897-4EED-BF6F-2EF299C67BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672D8820-8A99-43F3-9865-529FFF2F8953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3460" yWindow="4070" windowWidth="19200" windowHeight="11210" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3460" yWindow="4070" windowWidth="19200" windowHeight="11210" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,25 @@
     <sheet name="Shunts" sheetId="8" r:id="rId8"/>
     <sheet name="GameParameters" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="217">
   <si>
     <t>CIGRE European HV 13-Bus Benchmark — Dual-Price Stackelberg Reactive Power Market</t>
   </si>
@@ -582,9 +595,6 @@
     <t>eps_sequence</t>
   </si>
   <si>
-    <t>1e-2,1e-4,1e-6</t>
-  </si>
-  <si>
     <t>FB smoothing continuation (descending, comma-sep)</t>
   </si>
   <si>
@@ -676,6 +686,12 @@
   </si>
   <si>
     <t>ExtGrid</t>
+  </si>
+  <si>
+    <t>1e-2,1e-4,1e-6,1e-8</t>
+  </si>
+  <si>
+    <t>delta_reg</t>
   </si>
 </sst>
 </file>
@@ -789,11 +805,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1389,7 +1405,7 @@
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C67" s="13"/>
@@ -1432,7 +1448,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C2" s="13"/>
@@ -1911,7 +1927,7 @@
       <c r="L17" s="2"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="13"/>
@@ -1954,7 +1970,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="13"/>
@@ -2394,7 +2410,7 @@
       <c r="O13" s="2"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C17" s="13"/>
@@ -2444,7 +2460,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>105</v>
       </c>
       <c r="C2" s="13"/>
@@ -2912,7 +2928,7 @@
       <c r="V10" s="8"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="13"/>
@@ -2960,7 +2976,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>130</v>
       </c>
       <c r="C2" s="13"/>
@@ -3186,7 +3202,7 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C15" s="13"/>
@@ -3223,7 +3239,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>144</v>
       </c>
       <c r="C2" s="13"/>
@@ -3264,10 +3280,10 @@
         <v>146</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>147</v>
@@ -3305,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D5" s="7">
         <v>10</v>
@@ -3341,10 +3357,10 @@
         <v>0</v>
       </c>
       <c r="O5" s="7">
-        <v>1.8E-3</v>
+        <v>1.2000000000000001E-3</v>
       </c>
       <c r="P5" s="7">
-        <v>1.85</v>
+        <v>1.0499999999999998</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
@@ -3395,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="5">
-        <v>1.5E-3</v>
+        <v>3.7499999999999999E-3</v>
       </c>
       <c r="P6" s="5">
-        <v>1.1499999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" s="5">
         <v>0</v>
@@ -3449,10 +3465,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="P7" s="7">
-        <v>1.75</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="Q7" s="7">
         <v>0</v>
@@ -3503,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="5">
-        <v>2E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="P8" s="5">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="5">
         <v>0</v>
@@ -3517,7 +3533,7 @@
       <c r="S8" s="5"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="13"/>
@@ -3605,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D5" s="7">
         <v>8</v>
@@ -3625,7 +3641,7 @@
       <c r="I5" s="7"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C9" s="13"/>
@@ -3660,7 +3676,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>163</v>
       </c>
       <c r="C2" s="13"/>
@@ -3817,7 +3833,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="13"/>
@@ -3852,7 +3868,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>171</v>
       </c>
       <c r="C2" s="13"/>
@@ -3918,135 +3934,144 @@
         <v>183</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>187</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C12" s="7">
         <v>3000</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C13" s="5">
         <v>1E-8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C14" s="7">
         <v>300</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="C15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="C16" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C17" s="5">
         <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>205</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>211</v>
-      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="D21" s="2"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="13"/>
@@ -4058,5 +4083,6 @@
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/CIGRE_HV_Network_Input.xlsx
+++ b/data/CIGRE_HV_Network_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_MPEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672D8820-8A99-43F3-9865-529FFF2F8953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2C45F7-F29A-45BD-9EDF-BF2745A3A4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3460" yWindow="4070" windowWidth="19200" windowHeight="11210" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15225" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -805,11 +805,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1119,13 +1119,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:F67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -1134,278 +1134,278 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B67" s="12" t="s">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C67" s="13"/>
@@ -1435,20 +1435,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:L21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C2" s="13"/>
@@ -1462,7 +1462,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>57</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="7">
         <v>10</v>
       </c>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>11</v>
       </c>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="7">
         <v>12</v>
       </c>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>13</v>
       </c>
@@ -1926,8 +1926,8 @@
       </c>
       <c r="L17" s="2"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="12" t="s">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="13"/>
@@ -1953,7 +1953,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:O17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1969,8 +1969,8 @@
     <col min="15" max="15" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="13"/>
@@ -1987,7 +1987,7 @@
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
     </row>
-    <row r="4" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>85</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>8</v>
       </c>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -2409,8 +2409,8 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="12" t="s">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C17" s="13"/>
@@ -2439,7 +2439,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:V14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2459,8 +2459,8 @@
     <col min="22" max="22" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:22" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>105</v>
       </c>
       <c r="C2" s="13"/>
@@ -2484,7 +2484,7 @@
       <c r="U2" s="13"/>
       <c r="V2" s="13"/>
     </row>
-    <row r="4" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>106</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="V6" s="8"/>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="V8" s="8"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>6</v>
       </c>
@@ -2927,8 +2927,8 @@
       </c>
       <c r="V10" s="8"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B14" s="12" t="s">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="13"/>
@@ -2964,7 +2964,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2975,8 +2975,8 @@
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>130</v>
       </c>
       <c r="C2" s="13"/>
@@ -2990,7 +2990,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>131</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>143</v>
       </c>
@@ -3201,8 +3201,8 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="12" t="s">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C15" s="13"/>
@@ -3228,18 +3228,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:S11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="11.453125" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" customWidth="1"/>
     <col min="10" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>144</v>
       </c>
       <c r="C2" s="13"/>
@@ -3260,7 +3260,7 @@
       <c r="R2" s="13"/>
       <c r="S2" s="13"/>
     </row>
-    <row r="4" spans="2:19" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="S5" s="8"/>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="S6" s="5"/>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="S7" s="8"/>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>4</v>
       </c>
@@ -3532,8 +3532,8 @@
       </c>
       <c r="S8" s="5"/>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B11" s="12" t="s">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="13"/>
@@ -3566,19 +3566,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:I9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" customWidth="1"/>
-    <col min="8" max="8" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
     <col min="9" max="9" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="16" t="s">
         <v>158</v>
       </c>
@@ -3590,7 +3590,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
-    <row r="4" spans="2:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>159</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3640,8 +3640,8 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C9" s="13"/>
@@ -3664,7 +3664,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:L13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3675,8 +3675,8 @@
     <col min="12" max="12" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C2" s="13"/>
@@ -3690,7 +3690,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="4" spans="2:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>164</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2</v>
       </c>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>170</v>
       </c>
@@ -3832,8 +3832,8 @@
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="12" t="s">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="13"/>
@@ -3859,7 +3859,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:D24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3867,14 +3867,14 @@
     <col min="4" max="4" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>171</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
     </row>
-    <row r="4" spans="2:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>172</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>175</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>177</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>179</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>181</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>183</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>185</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>188</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>191</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>193</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>195</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>197</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>199</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>201</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
         <v>203</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>206</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
         <v>208</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>216</v>
       </c>
@@ -4070,8 +4070,8 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="12" t="s">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="13"/>

--- a/data/CIGRE_HV_Network_Input.xlsx
+++ b/data/CIGRE_HV_Network_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papaf\PycharmProjects\Stackelberg_MPEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2C45F7-F29A-45BD-9EDF-BF2745A3A4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A4A06A-EBAD-4D16-BA5C-75CE74DA68F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15225" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="38700" windowHeight="15225" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1739,7 +1739,7 @@
         <v>380</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>70</v>
@@ -1805,7 +1805,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>70</v>
